--- a/intake_forms/019_child_health_initiative_application_form--intake_forms.xlsx
+++ b/intake_forms/019_child_health_initiative_application_form--intake_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -912,8 +912,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -941,12 +941,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'nutrition_and_meal_support',_'value':_'nutrition'}</t>
+          <t>nutrition_and_meal_support</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Nutrition and Meal Support', 'value': 'nutrition'}</t>
+          <t>Nutrition and Meal Support</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'dental_health_access',_'value':_'dental'}</t>
+          <t>dental_health_access</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Dental Health Access', 'value': 'dental'}</t>
+          <t>Dental Health Access</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'mental_wellness_services',_'value':_'mental'}</t>
+          <t>mental_wellness_services</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Mental Wellness Services', 'value': 'mental'}</t>
+          <t>Mental Wellness Services</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'physical_fitness_grants',_'value':_'fitness'}</t>
+          <t>physical_fitness_grants</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Physical Fitness Grants', 'value': 'fitness'}</t>
+          <t>Physical Fitness Grants</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'under_$30,000',_'value':_'low'}</t>
+          <t>under_$30,000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Under $30,000', 'value': 'low'}</t>
+          <t>Under $30,000</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'$30,000_to_$60,000',_'value':_'medium'}</t>
+          <t>$30,000_to_$60,000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '$30,000 to $60,000', 'value': 'medium'}</t>
+          <t>$30,000 to $60,000</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'above_$60,000',_'value':_'high'}</t>
+          <t>above_$60,000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Above $60,000', 'value': 'high'}</t>
+          <t>Above $60,000</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'1_to_2',_'value':_'small'}</t>
+          <t>1_to_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '1 to 2', 'value': 'small'}</t>
+          <t>1 to 2</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'3_to_4',_'value':_'medium'}</t>
+          <t>3_to_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '3 to 4', 'value': 'medium'}</t>
+          <t>3 to 4</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'5_or_more',_'value':_'large'}</t>
+          <t>5_or_more</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '5 or more', 'value': 'large'}</t>
+          <t>5 or more</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree',_'value':_true}</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'I Agree', 'value': True}</t>
+          <t>I Agree</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'i_disagree',_'value':_false}</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'I Disagree', 'value': False}</t>
+          <t>I Disagree</t>
         </is>
       </c>
     </row>
